--- a/files/Sport-UI-Type.xlsx
+++ b/files/Sport-UI-Type.xlsx
@@ -2113,14 +2113,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2138,13 +2131,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2313,7 +2299,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2323,12 +2309,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2519,7 +2499,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -2656,15 +2636,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -2793,234 +2764,207 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3437,13 +3381,13 @@
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="6"/>
@@ -3452,196 +3396,196 @@
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="6"/>
     </row>
     <row r="9" ht="15" spans="1:5">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="6"/>
     </row>
     <row r="10" ht="25.2" customHeight="1" spans="1:5">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="6"/>
     </row>
     <row r="11" ht="15" spans="1:5">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="11"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" ht="15" spans="1:5">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="11"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" ht="15" spans="1:5">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="11"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" ht="15" spans="1:5">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" ht="15" spans="1:5">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="11"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" ht="15" spans="1:5">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="11"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" ht="15" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="11"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" ht="15" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="11"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" ht="15" spans="1:5">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="11"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" ht="15" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="11"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" ht="15" spans="1:5">
       <c r="A21" s="3" t="s">
@@ -3650,103 +3594,103 @@
       <c r="B21" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" ht="15" spans="1:5">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="11"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" ht="22.8" customHeight="1" spans="1:5">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E23" s="11"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" ht="15" spans="1:5">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="11"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" ht="15" spans="1:5">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="11"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" ht="15" spans="1:5">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="11"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" ht="15" spans="1:5">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E27" s="11"/>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" ht="15" spans="1:5">
       <c r="A28" s="3" t="s">
@@ -3755,2368 +3699,2368 @@
       <c r="B28" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E28" s="11"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" ht="15" spans="1:5">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E29" s="11"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" ht="15" spans="1:5">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E30" s="11"/>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" ht="15" spans="1:5">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" ht="15" spans="1:5">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="3" t="s">
         <v>100</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E32" s="11"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" ht="15" spans="1:5">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="3" t="s">
         <v>103</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="11"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" ht="15" spans="1:5">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="E34" s="11"/>
+      <c r="E34" s="10"/>
     </row>
     <row r="35" ht="15" spans="1:5">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E35" s="11"/>
+      <c r="E35" s="10"/>
     </row>
     <row r="36" ht="15" spans="1:5">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E36" s="11"/>
+      <c r="E36" s="10"/>
     </row>
     <row r="37" ht="15" spans="1:5">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E37" s="11"/>
+      <c r="E37" s="10"/>
     </row>
     <row r="38" ht="14.4" customHeight="1" spans="1:5">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E38" s="11"/>
+      <c r="E38" s="10"/>
     </row>
     <row r="39" ht="15" spans="1:5">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="E39" s="16"/>
+      <c r="E39" s="15"/>
     </row>
     <row r="40" ht="14.25" spans="1:5">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E40" s="16"/>
+      <c r="E40" s="15"/>
     </row>
     <row r="41" ht="14.25" spans="1:5">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E41" s="16"/>
+      <c r="E41" s="15"/>
     </row>
     <row r="42" ht="14.25" spans="1:5">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D42" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="E42" s="16"/>
+      <c r="E42" s="15"/>
     </row>
     <row r="43" ht="14.25" spans="1:5">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C43" s="20" t="s">
+      <c r="C43" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="E43" s="16"/>
+      <c r="E43" s="15"/>
     </row>
     <row r="44" ht="14.25" spans="1:5">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="20" t="s">
+      <c r="C44" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D44" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E44" s="16"/>
+      <c r="E44" s="15"/>
     </row>
     <row r="45" ht="14.25" spans="1:5">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="C45" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="E45" s="16"/>
+      <c r="E45" s="15"/>
     </row>
     <row r="46" ht="14.25" spans="1:5">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="E46" s="16"/>
+      <c r="E46" s="15"/>
     </row>
     <row r="47" ht="14.25" spans="1:5">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="C47" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="E47" s="16"/>
+      <c r="E47" s="15"/>
     </row>
     <row r="48" ht="15" spans="1:5">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="C48" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E48" s="16"/>
+      <c r="E48" s="15"/>
     </row>
     <row r="49" ht="15" spans="1:5">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="C49" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="E49" s="11"/>
+      <c r="E49" s="10"/>
     </row>
     <row r="50" ht="15" spans="1:5">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="E50" s="11"/>
+      <c r="E50" s="10"/>
     </row>
     <row r="51" ht="15" spans="1:5">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C51" s="20" t="s">
+      <c r="C51" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E51" s="11"/>
+      <c r="E51" s="10"/>
     </row>
     <row r="52" ht="15" spans="1:5">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E52" s="11"/>
+      <c r="E52" s="10"/>
     </row>
     <row r="53" ht="15" spans="1:5">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="C53" s="20" t="s">
+      <c r="C53" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="E53" s="11"/>
+      <c r="E53" s="10"/>
     </row>
     <row r="54" ht="15" spans="1:5">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="B54" s="21" t="s">
+      <c r="B54" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="C54" s="20" t="s">
+      <c r="C54" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="E54" s="11"/>
+      <c r="E54" s="10"/>
     </row>
     <row r="55" ht="15" spans="1:5">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="C55" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="E55" s="11"/>
+      <c r="E55" s="10"/>
     </row>
     <row r="56" ht="15" spans="1:5">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="C56" s="20" t="s">
+      <c r="C56" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E56" s="11"/>
+      <c r="E56" s="10"/>
     </row>
     <row r="57" ht="15" spans="1:5">
-      <c r="A57" s="14" t="s">
+      <c r="A57" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C57" s="20" t="s">
+      <c r="C57" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="D57" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="E57" s="11"/>
+      <c r="E57" s="10"/>
     </row>
     <row r="58" ht="15" spans="1:5">
-      <c r="A58" s="14" t="s">
+      <c r="A58" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="C58" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="E58" s="11"/>
+      <c r="E58" s="10"/>
     </row>
     <row r="59" ht="17.4" customHeight="1" spans="1:5">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="C59" s="20" t="s">
+      <c r="C59" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="D59" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="E59" s="11"/>
+      <c r="E59" s="10"/>
     </row>
     <row r="60" ht="15" spans="1:5">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="C60" s="20" t="s">
+      <c r="C60" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D60" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E60" s="11"/>
+      <c r="E60" s="10"/>
     </row>
     <row r="61" ht="15" spans="1:5">
-      <c r="A61" s="14" t="s">
+      <c r="A61" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="C61" s="20" t="s">
+      <c r="C61" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="D61" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="E61" s="11"/>
+      <c r="E61" s="10"/>
     </row>
     <row r="62" ht="15" spans="1:5">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="C62" s="20" t="s">
+      <c r="C62" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D62" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="E62" s="11"/>
+      <c r="E62" s="10"/>
     </row>
     <row r="63" ht="15" spans="1:5">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="C63" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D63" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="E63" s="11"/>
+      <c r="E63" s="10"/>
     </row>
     <row r="64" ht="15" spans="1:5">
-      <c r="A64" s="14" t="s">
+      <c r="A64" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="B64" s="14" t="s">
+      <c r="B64" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="C64" s="20" t="s">
+      <c r="C64" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="D64" s="10" t="s">
+      <c r="D64" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E64" s="11"/>
+      <c r="E64" s="10"/>
     </row>
     <row r="65" ht="15" spans="1:5">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C65" s="20" t="s">
+      <c r="C65" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="D65" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="E65" s="11"/>
+      <c r="E65" s="10"/>
     </row>
     <row r="66" ht="15" spans="1:5">
-      <c r="A66" s="14" t="s">
+      <c r="A66" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C66" s="20" t="s">
+      <c r="C66" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="D66" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="E66" s="11"/>
+      <c r="E66" s="10"/>
     </row>
     <row r="67" ht="15" spans="1:5">
-      <c r="A67" s="14" t="s">
+      <c r="A67" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="B67" s="14" t="s">
+      <c r="B67" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="C67" s="20" t="s">
+      <c r="C67" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="D67" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="E67" s="11"/>
+      <c r="E67" s="10"/>
     </row>
     <row r="68" ht="15" spans="1:5">
-      <c r="A68" s="14" t="s">
+      <c r="A68" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="C68" s="20" t="s">
+      <c r="C68" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="D68" s="10" t="s">
+      <c r="D68" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="E68" s="11"/>
+      <c r="E68" s="10"/>
     </row>
     <row r="69" ht="15" spans="1:5">
-      <c r="A69" s="14" t="s">
+      <c r="A69" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="C69" s="20" t="s">
+      <c r="C69" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="D69" s="10" t="s">
+      <c r="D69" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="E69" s="11"/>
+      <c r="E69" s="10"/>
     </row>
     <row r="70" ht="15" spans="1:5">
-      <c r="A70" s="14" t="s">
+      <c r="A70" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="C70" s="20" t="s">
+      <c r="C70" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="D70" s="10" t="s">
+      <c r="D70" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="E70" s="11"/>
+      <c r="E70" s="10"/>
     </row>
     <row r="71" ht="15" spans="1:5">
-      <c r="A71" s="14" t="s">
+      <c r="A71" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="B71" s="14" t="s">
+      <c r="B71" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="C71" s="20" t="s">
+      <c r="C71" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="D71" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="E71" s="11"/>
+      <c r="E71" s="10"/>
     </row>
     <row r="72" ht="15" spans="1:5">
-      <c r="A72" s="14" t="s">
+      <c r="A72" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="B72" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C72" s="20" t="s">
+      <c r="C72" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="D72" s="10" t="s">
+      <c r="D72" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E72" s="11"/>
+      <c r="E72" s="10"/>
     </row>
     <row r="73" ht="15" spans="1:5">
-      <c r="A73" s="14" t="s">
+      <c r="A73" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="B73" s="14" t="s">
+      <c r="B73" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="C73" s="20" t="s">
+      <c r="C73" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="D73" s="10" t="s">
+      <c r="D73" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="E73" s="11"/>
+      <c r="E73" s="10"/>
     </row>
     <row r="74" ht="15" spans="1:5">
-      <c r="A74" s="14" t="s">
+      <c r="A74" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B74" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="C74" s="20" t="s">
+      <c r="C74" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D74" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="E74" s="11"/>
+      <c r="E74" s="10"/>
     </row>
     <row r="75" ht="15" spans="1:5">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="B75" s="21" t="s">
+      <c r="B75" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="C75" s="20" t="s">
+      <c r="C75" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="D75" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="E75" s="11"/>
+      <c r="E75" s="10"/>
     </row>
     <row r="76" ht="15" spans="1:5">
-      <c r="A76" s="14" t="s">
+      <c r="A76" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="B76" s="22" t="s">
+      <c r="B76" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="C76" s="20" t="s">
+      <c r="C76" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E76" s="11"/>
+      <c r="E76" s="10"/>
     </row>
     <row r="77" ht="15" spans="1:5">
-      <c r="A77" s="14" t="s">
+      <c r="A77" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="B77" s="22" t="s">
+      <c r="B77" s="21" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="20" t="s">
+      <c r="C77" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="D77" s="10" t="s">
+      <c r="D77" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="E77" s="11"/>
+      <c r="E77" s="10"/>
     </row>
     <row r="78" ht="15" spans="1:5">
-      <c r="A78" s="14" t="s">
+      <c r="A78" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="B78" s="22" t="s">
+      <c r="B78" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="C78" s="20" t="s">
+      <c r="C78" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="D78" s="10" t="s">
+      <c r="D78" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="E78" s="11"/>
+      <c r="E78" s="10"/>
     </row>
     <row r="79" ht="15" spans="1:5">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="B79" s="22" t="s">
+      <c r="B79" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C79" s="20" t="s">
+      <c r="C79" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="D79" s="10" t="s">
+      <c r="D79" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="E79" s="11"/>
+      <c r="E79" s="10"/>
     </row>
     <row r="80" ht="15" spans="1:5">
-      <c r="A80" s="22" t="s">
+      <c r="A80" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="B80" s="22" t="s">
+      <c r="B80" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="C80" s="20" t="s">
+      <c r="C80" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="D80" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E80" s="11"/>
+      <c r="E80" s="10"/>
     </row>
     <row r="81" ht="15" spans="1:5">
-      <c r="A81" s="22" t="s">
+      <c r="A81" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="B81" s="22" t="s">
+      <c r="B81" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="C81" s="20" t="s">
+      <c r="C81" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="D81" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="E81" s="11"/>
+      <c r="E81" s="10"/>
     </row>
     <row r="82" ht="15" spans="1:5">
-      <c r="A82" s="22" t="s">
+      <c r="A82" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="B82" s="22" t="s">
+      <c r="B82" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="C82" s="20" t="s">
+      <c r="C82" s="19" t="s">
         <v>291</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="D82" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="E82" s="11"/>
+      <c r="E82" s="10"/>
     </row>
     <row r="83" ht="15" spans="1:5">
-      <c r="A83" s="22" t="s">
+      <c r="A83" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="B83" s="22" t="s">
+      <c r="B83" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="C83" s="20" t="s">
+      <c r="C83" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="D83" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="E83" s="11"/>
+      <c r="E83" s="10"/>
     </row>
     <row r="84" ht="15" spans="1:5">
-      <c r="A84" s="22" t="s">
+      <c r="A84" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="B84" s="22" t="s">
+      <c r="B84" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="C84" s="20" t="s">
+      <c r="C84" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="D84" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="E84" s="11"/>
+      <c r="E84" s="10"/>
     </row>
     <row r="85" ht="15" spans="1:5">
-      <c r="A85" s="22" t="s">
+      <c r="A85" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="B85" s="22" t="s">
+      <c r="B85" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="C85" s="20" t="s">
+      <c r="C85" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="D85" s="10" t="s">
+      <c r="D85" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E85" s="11"/>
+      <c r="E85" s="10"/>
     </row>
     <row r="86" ht="15" spans="1:5">
-      <c r="A86" s="22" t="s">
+      <c r="A86" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="B86" s="22" t="s">
+      <c r="B86" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="C86" s="20" t="s">
+      <c r="C86" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="D86" s="10" t="s">
+      <c r="D86" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="E86" s="11"/>
+      <c r="E86" s="10"/>
     </row>
     <row r="87" ht="15" spans="1:5">
-      <c r="A87" s="22" t="s">
+      <c r="A87" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="B87" s="22" t="s">
+      <c r="B87" s="21" t="s">
         <v>310</v>
       </c>
-      <c r="C87" s="20" t="s">
+      <c r="C87" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="D87" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="E87" s="11"/>
+      <c r="E87" s="10"/>
     </row>
     <row r="88" ht="15" spans="1:5">
-      <c r="A88" s="22" t="s">
+      <c r="A88" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="B88" s="23" t="s">
+      <c r="B88" s="22" t="s">
         <v>314</v>
       </c>
-      <c r="C88" s="20" t="s">
+      <c r="C88" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="D88" s="10" t="s">
+      <c r="D88" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E88" s="11"/>
+      <c r="E88" s="10"/>
     </row>
     <row r="89" ht="15" spans="1:5">
-      <c r="A89" s="22" t="s">
+      <c r="A89" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="B89" s="22" t="s">
+      <c r="B89" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="C89" s="20" t="s">
+      <c r="C89" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="D89" s="10" t="s">
+      <c r="D89" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="E89" s="11"/>
+      <c r="E89" s="10"/>
     </row>
     <row r="90" ht="15" spans="1:5">
-      <c r="A90" s="22" t="s">
+      <c r="A90" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B90" s="22" t="s">
+      <c r="B90" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="C90" s="20" t="s">
+      <c r="C90" s="19" t="s">
         <v>322</v>
       </c>
-      <c r="D90" s="10" t="s">
+      <c r="D90" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="E90" s="11"/>
+      <c r="E90" s="10"/>
     </row>
     <row r="91" ht="15" spans="1:5">
-      <c r="A91" s="22" t="s">
+      <c r="A91" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="B91" s="22" t="s">
+      <c r="B91" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="C91" s="20" t="s">
+      <c r="C91" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="D91" s="10" t="s">
+      <c r="D91" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="E91" s="11"/>
+      <c r="E91" s="10"/>
     </row>
     <row r="92" ht="15" spans="1:5">
-      <c r="A92" s="22" t="s">
+      <c r="A92" s="21" t="s">
         <v>328</v>
       </c>
-      <c r="B92" s="22" t="s">
+      <c r="B92" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="C92" s="20" t="s">
+      <c r="C92" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="D92" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="E92" s="11"/>
+      <c r="E92" s="10"/>
     </row>
     <row r="93" ht="15" spans="1:5">
-      <c r="A93" s="22" t="s">
+      <c r="A93" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="B93" s="22" t="s">
+      <c r="B93" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="C93" s="20" t="s">
+      <c r="C93" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="D93" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="E93" s="11"/>
+      <c r="E93" s="10"/>
     </row>
     <row r="94" ht="15" spans="1:5">
-      <c r="A94" s="22" t="s">
+      <c r="A94" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="B94" s="22" t="s">
+      <c r="B94" s="21" t="s">
         <v>337</v>
       </c>
-      <c r="C94" s="20" t="s">
+      <c r="C94" s="19" t="s">
         <v>338</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="D94" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="E94" s="11"/>
+      <c r="E94" s="10"/>
     </row>
     <row r="95" ht="15" spans="1:5">
-      <c r="A95" s="22" t="s">
+      <c r="A95" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="B95" s="22" t="s">
+      <c r="B95" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="C95" s="20" t="s">
+      <c r="C95" s="19" t="s">
         <v>342</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="D95" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="E95" s="11"/>
+      <c r="E95" s="10"/>
     </row>
     <row r="96" ht="15" spans="1:5">
-      <c r="A96" s="22" t="s">
+      <c r="A96" s="21" t="s">
         <v>344</v>
       </c>
-      <c r="B96" s="22" t="s">
+      <c r="B96" s="21" t="s">
         <v>345</v>
       </c>
-      <c r="C96" s="20" t="s">
+      <c r="C96" s="19" t="s">
         <v>346</v>
       </c>
-      <c r="D96" s="10" t="s">
+      <c r="D96" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E96" s="11"/>
+      <c r="E96" s="10"/>
     </row>
     <row r="97" ht="15" spans="1:5">
-      <c r="A97" s="22" t="s">
+      <c r="A97" s="21" t="s">
         <v>347</v>
       </c>
-      <c r="B97" s="22" t="s">
+      <c r="B97" s="21" t="s">
         <v>348</v>
       </c>
-      <c r="C97" s="20" t="s">
+      <c r="C97" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="D97" s="10" t="s">
+      <c r="D97" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="E97" s="11"/>
+      <c r="E97" s="10"/>
     </row>
     <row r="98" ht="15" spans="1:5">
-      <c r="A98" s="22" t="s">
+      <c r="A98" s="21" t="s">
         <v>351</v>
       </c>
-      <c r="B98" s="22" t="s">
+      <c r="B98" s="21" t="s">
         <v>352</v>
       </c>
-      <c r="C98" s="20" t="s">
+      <c r="C98" s="19" t="s">
         <v>353</v>
       </c>
-      <c r="D98" s="10" t="s">
+      <c r="D98" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E98" s="11"/>
+      <c r="E98" s="10"/>
     </row>
     <row r="99" ht="15" spans="1:5">
-      <c r="A99" s="22" t="s">
+      <c r="A99" s="21" t="s">
         <v>355</v>
       </c>
-      <c r="B99" s="22" t="s">
+      <c r="B99" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="C99" s="20" t="s">
+      <c r="C99" s="19" t="s">
         <v>357</v>
       </c>
-      <c r="D99" s="10" t="s">
+      <c r="D99" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="E99" s="11"/>
+      <c r="E99" s="10"/>
     </row>
     <row r="100" ht="15" spans="1:5">
-      <c r="A100" s="22" t="s">
+      <c r="A100" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="B100" s="22" t="s">
+      <c r="B100" s="21" t="s">
         <v>360</v>
       </c>
-      <c r="C100" s="20" t="s">
+      <c r="C100" s="19" t="s">
         <v>361</v>
       </c>
-      <c r="D100" s="10" t="s">
+      <c r="D100" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="E100" s="11"/>
+      <c r="E100" s="10"/>
     </row>
     <row r="101" ht="15" spans="1:5">
-      <c r="A101" s="22" t="s">
+      <c r="A101" s="21" t="s">
         <v>363</v>
       </c>
-      <c r="B101" s="22" t="s">
+      <c r="B101" s="21" t="s">
         <v>364</v>
       </c>
-      <c r="C101" s="20" t="s">
+      <c r="C101" s="19" t="s">
         <v>365</v>
       </c>
-      <c r="D101" s="10" t="s">
+      <c r="D101" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="E101" s="11"/>
+      <c r="E101" s="10"/>
     </row>
     <row r="102" ht="15" spans="1:5">
-      <c r="A102" s="22" t="s">
+      <c r="A102" s="21" t="s">
         <v>367</v>
       </c>
-      <c r="B102" s="22" t="s">
+      <c r="B102" s="21" t="s">
         <v>368</v>
       </c>
-      <c r="C102" s="20" t="s">
+      <c r="C102" s="19" t="s">
         <v>369</v>
       </c>
-      <c r="D102" s="10" t="s">
+      <c r="D102" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="E102" s="11"/>
+      <c r="E102" s="10"/>
     </row>
     <row r="103" ht="15" spans="1:5">
-      <c r="A103" s="22" t="s">
+      <c r="A103" s="21" t="s">
         <v>371</v>
       </c>
-      <c r="B103" s="22" t="s">
+      <c r="B103" s="21" t="s">
         <v>372</v>
       </c>
-      <c r="C103" s="20" t="s">
+      <c r="C103" s="19" t="s">
         <v>373</v>
       </c>
-      <c r="D103" s="10" t="s">
+      <c r="D103" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="E103" s="11"/>
+      <c r="E103" s="10"/>
     </row>
     <row r="104" ht="15" spans="1:5">
-      <c r="A104" s="22" t="s">
+      <c r="A104" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="B104" s="22" t="s">
+      <c r="B104" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="C104" s="20" t="s">
+      <c r="C104" s="19" t="s">
         <v>377</v>
       </c>
-      <c r="D104" s="10" t="s">
+      <c r="D104" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E104" s="11"/>
+      <c r="E104" s="10"/>
     </row>
     <row r="105" ht="15" spans="1:5">
-      <c r="A105" s="22" t="s">
+      <c r="A105" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="B105" s="22" t="s">
+      <c r="B105" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="C105" s="20" t="s">
+      <c r="C105" s="19" t="s">
         <v>380</v>
       </c>
-      <c r="D105" s="10" t="s">
+      <c r="D105" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="E105" s="11"/>
+      <c r="E105" s="10"/>
     </row>
     <row r="106" ht="15" spans="1:5">
-      <c r="A106" s="22" t="s">
+      <c r="A106" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="B106" s="22" t="s">
+      <c r="B106" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="C106" s="20" t="s">
+      <c r="C106" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="D106" s="10" t="s">
+      <c r="D106" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="E106" s="11"/>
+      <c r="E106" s="10"/>
     </row>
     <row r="107" ht="15" spans="1:5">
-      <c r="A107" s="22" t="s">
+      <c r="A107" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="B107" s="22" t="s">
+      <c r="B107" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="C107" s="20" t="s">
+      <c r="C107" s="19" t="s">
         <v>388</v>
       </c>
-      <c r="D107" s="10" t="s">
+      <c r="D107" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="E107" s="11"/>
+      <c r="E107" s="10"/>
     </row>
     <row r="108" ht="15" spans="1:5">
-      <c r="A108" s="22" t="s">
+      <c r="A108" s="21" t="s">
         <v>390</v>
       </c>
-      <c r="B108" s="22" t="s">
+      <c r="B108" s="21" t="s">
         <v>391</v>
       </c>
-      <c r="C108" s="20" t="s">
+      <c r="C108" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="D108" s="10" t="s">
+      <c r="D108" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E108" s="11"/>
+      <c r="E108" s="10"/>
     </row>
     <row r="109" ht="15" spans="1:5">
-      <c r="A109" s="22" t="s">
+      <c r="A109" s="21" t="s">
         <v>393</v>
       </c>
-      <c r="B109" s="22" t="s">
+      <c r="B109" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C109" s="20" t="s">
+      <c r="C109" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="D109" s="10" t="s">
+      <c r="D109" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="E109" s="11"/>
+      <c r="E109" s="10"/>
     </row>
     <row r="110" ht="15" spans="1:5">
-      <c r="A110" s="22" t="s">
+      <c r="A110" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="B110" s="22" t="s">
+      <c r="B110" s="21" t="s">
         <v>397</v>
       </c>
-      <c r="C110" s="20" t="s">
+      <c r="C110" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="D110" s="10" t="s">
+      <c r="D110" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="E110" s="11"/>
+      <c r="E110" s="10"/>
     </row>
     <row r="111" ht="15" spans="1:5">
-      <c r="A111" s="22" t="s">
+      <c r="A111" s="21" t="s">
         <v>400</v>
       </c>
-      <c r="B111" s="22" t="s">
+      <c r="B111" s="21" t="s">
         <v>401</v>
       </c>
-      <c r="C111" s="20" t="s">
+      <c r="C111" s="19" t="s">
         <v>402</v>
       </c>
-      <c r="D111" s="10" t="s">
+      <c r="D111" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="E111" s="11"/>
+      <c r="E111" s="10"/>
     </row>
     <row r="112" ht="15" spans="1:5">
-      <c r="A112" s="22" t="s">
+      <c r="A112" s="21" t="s">
         <v>404</v>
       </c>
-      <c r="B112" s="22" t="s">
+      <c r="B112" s="21" t="s">
         <v>405</v>
       </c>
-      <c r="C112" s="20" t="s">
+      <c r="C112" s="19" t="s">
         <v>406</v>
       </c>
-      <c r="D112" s="10" t="s">
+      <c r="D112" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E112" s="11"/>
+      <c r="E112" s="10"/>
     </row>
     <row r="113" ht="15" spans="1:5">
-      <c r="A113" s="22" t="s">
+      <c r="A113" s="21" t="s">
         <v>407</v>
       </c>
-      <c r="B113" s="22" t="s">
+      <c r="B113" s="21" t="s">
         <v>408</v>
       </c>
-      <c r="C113" s="20" t="s">
+      <c r="C113" s="19" t="s">
         <v>409</v>
       </c>
-      <c r="D113" s="10" t="s">
+      <c r="D113" s="9" t="s">
         <v>410</v>
       </c>
-      <c r="E113" s="11"/>
+      <c r="E113" s="10"/>
     </row>
     <row r="114" ht="15" spans="1:5">
-      <c r="A114" s="22" t="s">
+      <c r="A114" s="21" t="s">
         <v>411</v>
       </c>
-      <c r="B114" s="22" t="s">
+      <c r="B114" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="C114" s="20" t="s">
+      <c r="C114" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="D114" s="10" t="s">
+      <c r="D114" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="E114" s="11"/>
+      <c r="E114" s="10"/>
     </row>
     <row r="115" ht="15" spans="1:5">
-      <c r="A115" s="22" t="s">
+      <c r="A115" s="21" t="s">
         <v>415</v>
       </c>
-      <c r="B115" s="22" t="s">
+      <c r="B115" s="21" t="s">
         <v>416</v>
       </c>
-      <c r="C115" s="20" t="s">
+      <c r="C115" s="19" t="s">
         <v>417</v>
       </c>
-      <c r="D115" s="10" t="s">
+      <c r="D115" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="E115" s="11"/>
+      <c r="E115" s="10"/>
     </row>
     <row r="116" ht="15" spans="1:5">
-      <c r="A116" s="22" t="s">
+      <c r="A116" s="21" t="s">
         <v>419</v>
       </c>
-      <c r="B116" s="23" t="s">
+      <c r="B116" s="22" t="s">
         <v>420</v>
       </c>
-      <c r="C116" s="20" t="s">
+      <c r="C116" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="D116" s="10" t="s">
+      <c r="D116" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E116" s="11"/>
+      <c r="E116" s="10"/>
     </row>
     <row r="117" ht="15" spans="1:5">
-      <c r="A117" s="22" t="s">
+      <c r="A117" s="21" t="s">
         <v>422</v>
       </c>
-      <c r="B117" s="23" t="s">
+      <c r="B117" s="22" t="s">
         <v>423</v>
       </c>
-      <c r="C117" s="20" t="s">
+      <c r="C117" s="19" t="s">
         <v>424</v>
       </c>
-      <c r="D117" s="10" t="s">
+      <c r="D117" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="E117" s="11"/>
+      <c r="E117" s="10"/>
     </row>
     <row r="118" ht="15" spans="1:5">
-      <c r="A118" s="22" t="s">
+      <c r="A118" s="21" t="s">
         <v>426</v>
       </c>
-      <c r="B118" s="23" t="s">
+      <c r="B118" s="22" t="s">
         <v>427</v>
       </c>
-      <c r="C118" s="20" t="s">
+      <c r="C118" s="19" t="s">
         <v>428</v>
       </c>
-      <c r="D118" s="10" t="s">
+      <c r="D118" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="E118" s="11"/>
+      <c r="E118" s="10"/>
     </row>
     <row r="119" ht="15" spans="1:5">
-      <c r="A119" s="22" t="s">
+      <c r="A119" s="21" t="s">
         <v>430</v>
       </c>
-      <c r="B119" s="23" t="s">
+      <c r="B119" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="C119" s="20" t="s">
+      <c r="C119" s="19" t="s">
         <v>432</v>
       </c>
-      <c r="D119" s="10" t="s">
+      <c r="D119" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="E119" s="11"/>
+      <c r="E119" s="10"/>
     </row>
     <row r="120" ht="15" spans="1:5">
-      <c r="A120" s="22" t="s">
+      <c r="A120" s="21" t="s">
         <v>434</v>
       </c>
-      <c r="B120" s="23" t="s">
+      <c r="B120" s="22" t="s">
         <v>435</v>
       </c>
-      <c r="C120" s="20" t="s">
+      <c r="C120" s="19" t="s">
         <v>436</v>
       </c>
-      <c r="D120" s="10" t="s">
+      <c r="D120" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="11"/>
+      <c r="E120" s="10"/>
     </row>
     <row r="121" ht="15" spans="1:5">
-      <c r="A121" s="22" t="s">
+      <c r="A121" s="21" t="s">
         <v>437</v>
       </c>
-      <c r="B121" s="23" t="s">
+      <c r="B121" s="22" t="s">
         <v>438</v>
       </c>
-      <c r="C121" s="20" t="s">
+      <c r="C121" s="19" t="s">
         <v>439</v>
       </c>
-      <c r="D121" s="10" t="s">
+      <c r="D121" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="E121" s="11"/>
+      <c r="E121" s="10"/>
     </row>
     <row r="122" ht="15" spans="1:5">
-      <c r="A122" s="22" t="s">
+      <c r="A122" s="21" t="s">
         <v>441</v>
       </c>
-      <c r="B122" s="23" t="s">
+      <c r="B122" s="22" t="s">
         <v>442</v>
       </c>
-      <c r="C122" s="20" t="s">
+      <c r="C122" s="19" t="s">
         <v>443</v>
       </c>
-      <c r="D122" s="10" t="s">
+      <c r="D122" s="9" t="s">
         <v>444</v>
       </c>
-      <c r="E122" s="11"/>
+      <c r="E122" s="10"/>
     </row>
     <row r="123" ht="15" spans="1:5">
-      <c r="A123" s="24" t="s">
+      <c r="A123" s="22" t="s">
         <v>445</v>
       </c>
-      <c r="B123" s="25" t="s">
+      <c r="B123" s="22" t="s">
         <v>446</v>
       </c>
-      <c r="C123" s="25" t="s">
+      <c r="C123" s="22" t="s">
         <v>447</v>
       </c>
-      <c r="D123" s="26" t="s">
+      <c r="D123" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="E123" s="27"/>
+      <c r="E123" s="10"/>
     </row>
     <row r="124" ht="15" spans="1:5">
-      <c r="A124" s="24" t="s">
+      <c r="A124" s="22" t="s">
         <v>449</v>
       </c>
-      <c r="B124" s="28" t="s">
+      <c r="B124" s="22" t="s">
         <v>450</v>
       </c>
-      <c r="C124" s="25" t="s">
+      <c r="C124" s="22" t="s">
         <v>451</v>
       </c>
-      <c r="D124" s="26" t="s">
+      <c r="D124" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="E124" s="27"/>
+      <c r="E124" s="10"/>
     </row>
     <row r="125" ht="15" spans="1:5">
-      <c r="A125" s="24" t="s">
+      <c r="A125" s="22" t="s">
         <v>452</v>
       </c>
-      <c r="B125" s="28" t="s">
+      <c r="B125" s="22" t="s">
         <v>453</v>
       </c>
-      <c r="C125" s="25" t="s">
+      <c r="C125" s="22" t="s">
         <v>454</v>
       </c>
-      <c r="D125" s="26" t="s">
+      <c r="D125" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="E125" s="27"/>
+      <c r="E125" s="10"/>
     </row>
     <row r="126" ht="15" spans="1:5">
-      <c r="A126" s="24" t="s">
+      <c r="A126" s="22" t="s">
         <v>456</v>
       </c>
-      <c r="B126" s="25" t="s">
+      <c r="B126" s="22" t="s">
         <v>457</v>
       </c>
-      <c r="C126" s="25" t="s">
+      <c r="C126" s="22" t="s">
         <v>458</v>
       </c>
-      <c r="D126" s="26" t="s">
+      <c r="D126" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="E126" s="27"/>
+      <c r="E126" s="10"/>
     </row>
     <row r="127" ht="15" spans="1:5">
-      <c r="A127" s="24" t="s">
+      <c r="A127" s="22" t="s">
         <v>460</v>
       </c>
-      <c r="B127" s="25" t="s">
+      <c r="B127" s="22" t="s">
         <v>461</v>
       </c>
-      <c r="C127" s="25" t="s">
+      <c r="C127" s="22" t="s">
         <v>462</v>
       </c>
-      <c r="D127" s="26" t="s">
+      <c r="D127" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="E127" s="27"/>
+      <c r="E127" s="10"/>
     </row>
     <row r="128" ht="15" spans="1:5">
-      <c r="A128" s="29" t="s">
+      <c r="A128" s="22" t="s">
         <v>464</v>
       </c>
-      <c r="B128" s="29" t="s">
+      <c r="B128" s="22" t="s">
         <v>465</v>
       </c>
-      <c r="C128" s="28" t="s">
+      <c r="C128" s="22" t="s">
         <v>466</v>
       </c>
-      <c r="D128" s="26" t="s">
+      <c r="D128" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E128" s="27"/>
+      <c r="E128" s="10"/>
     </row>
     <row r="129" ht="15" spans="1:5">
-      <c r="A129" s="24" t="s">
+      <c r="A129" s="22" t="s">
         <v>467</v>
       </c>
-      <c r="B129" s="24" t="s">
+      <c r="B129" s="22" t="s">
         <v>468</v>
       </c>
-      <c r="C129" s="30" t="s">
+      <c r="C129" s="22" t="s">
         <v>469</v>
       </c>
-      <c r="D129" s="26" t="s">
+      <c r="D129" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="E129" s="27"/>
+      <c r="E129" s="10"/>
     </row>
     <row r="130" ht="15" spans="1:5">
-      <c r="A130" s="24" t="s">
+      <c r="A130" s="22" t="s">
         <v>471</v>
       </c>
-      <c r="B130" s="24" t="s">
+      <c r="B130" s="22" t="s">
         <v>472</v>
       </c>
-      <c r="C130" s="28" t="s">
+      <c r="C130" s="22" t="s">
         <v>473</v>
       </c>
-      <c r="D130" s="26" t="s">
+      <c r="D130" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="E130" s="27"/>
+      <c r="E130" s="10"/>
     </row>
     <row r="131" ht="15" spans="1:5">
-      <c r="A131" s="24" t="s">
+      <c r="A131" s="22" t="s">
         <v>475</v>
       </c>
-      <c r="B131" s="24" t="s">
+      <c r="B131" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="C131" s="28" t="s">
+      <c r="C131" s="22" t="s">
         <v>477</v>
       </c>
-      <c r="D131" s="26" t="s">
+      <c r="D131" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="E131" s="27"/>
+      <c r="E131" s="10"/>
     </row>
     <row r="132" ht="15" spans="1:5">
-      <c r="A132" s="24" t="s">
+      <c r="A132" s="22" t="s">
         <v>479</v>
       </c>
-      <c r="B132" s="24" t="s">
+      <c r="B132" s="22" t="s">
         <v>480</v>
       </c>
-      <c r="C132" s="30" t="s">
+      <c r="C132" s="22" t="s">
         <v>481</v>
       </c>
-      <c r="D132" s="26" t="s">
+      <c r="D132" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E132" s="27"/>
+      <c r="E132" s="10"/>
     </row>
     <row r="133" ht="15" spans="1:5">
-      <c r="A133" s="24" t="s">
+      <c r="A133" s="22" t="s">
         <v>482</v>
       </c>
-      <c r="B133" s="24" t="s">
+      <c r="B133" s="22" t="s">
         <v>483</v>
       </c>
-      <c r="C133" s="28" t="s">
+      <c r="C133" s="22" t="s">
         <v>484</v>
       </c>
-      <c r="D133" s="26" t="s">
+      <c r="D133" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="E133" s="27"/>
+      <c r="E133" s="10"/>
     </row>
     <row r="134" ht="15" spans="1:5">
-      <c r="A134" s="24" t="s">
+      <c r="A134" s="22" t="s">
         <v>486</v>
       </c>
-      <c r="B134" s="24" t="s">
+      <c r="B134" s="22" t="s">
         <v>487</v>
       </c>
-      <c r="C134" s="28" t="s">
+      <c r="C134" s="22" t="s">
         <v>488</v>
       </c>
-      <c r="D134" s="26" t="s">
+      <c r="D134" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="E134" s="27"/>
+      <c r="E134" s="10"/>
     </row>
     <row r="135" ht="15" spans="1:5">
-      <c r="A135" s="24" t="s">
+      <c r="A135" s="22" t="s">
         <v>490</v>
       </c>
-      <c r="B135" s="24" t="s">
+      <c r="B135" s="22" t="s">
         <v>491</v>
       </c>
-      <c r="C135" s="30" t="s">
+      <c r="C135" s="22" t="s">
         <v>492</v>
       </c>
-      <c r="D135" s="26" t="s">
+      <c r="D135" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="E135" s="27"/>
+      <c r="E135" s="10"/>
     </row>
     <row r="136" ht="15" spans="1:5">
-      <c r="A136" s="24" t="s">
+      <c r="A136" s="22" t="s">
         <v>494</v>
       </c>
-      <c r="B136" s="24" t="s">
+      <c r="B136" s="22" t="s">
         <v>495</v>
       </c>
-      <c r="C136" s="28" t="s">
+      <c r="C136" s="22" t="s">
         <v>496</v>
       </c>
-      <c r="D136" s="26" t="s">
+      <c r="D136" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="E136" s="27"/>
+      <c r="E136" s="10"/>
     </row>
     <row r="137" ht="15" spans="1:5">
-      <c r="A137" s="24" t="s">
+      <c r="A137" s="22" t="s">
         <v>497</v>
       </c>
-      <c r="B137" s="24" t="s">
+      <c r="B137" s="22" t="s">
         <v>498</v>
       </c>
-      <c r="C137" s="28" t="s">
+      <c r="C137" s="22" t="s">
         <v>499</v>
       </c>
-      <c r="D137" s="26" t="s">
+      <c r="D137" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="E137" s="27"/>
+      <c r="E137" s="10"/>
     </row>
     <row r="138" ht="15" spans="1:5">
-      <c r="A138" s="24" t="s">
+      <c r="A138" s="22" t="s">
         <v>501</v>
       </c>
-      <c r="B138" s="24" t="s">
+      <c r="B138" s="22" t="s">
         <v>502</v>
       </c>
-      <c r="C138" s="30" t="s">
+      <c r="C138" s="22" t="s">
         <v>503</v>
       </c>
-      <c r="D138" s="26" t="s">
+      <c r="D138" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="E138" s="27"/>
+      <c r="E138" s="10"/>
     </row>
     <row r="139" ht="15" spans="1:5">
-      <c r="A139" s="24" t="s">
+      <c r="A139" s="22" t="s">
         <v>505</v>
       </c>
-      <c r="B139" s="24" t="s">
+      <c r="B139" s="22" t="s">
         <v>506</v>
       </c>
-      <c r="C139" s="28" t="s">
+      <c r="C139" s="22" t="s">
         <v>507</v>
       </c>
-      <c r="D139" s="26" t="s">
+      <c r="D139" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="E139" s="27"/>
+      <c r="E139" s="10"/>
     </row>
     <row r="140" ht="15" spans="1:5">
-      <c r="A140" s="24" t="s">
+      <c r="A140" s="22" t="s">
         <v>509</v>
       </c>
-      <c r="B140" s="24" t="s">
+      <c r="B140" s="22" t="s">
         <v>510</v>
       </c>
-      <c r="C140" s="28" t="s">
+      <c r="C140" s="22" t="s">
         <v>511</v>
       </c>
-      <c r="D140" s="26" t="s">
+      <c r="D140" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E140" s="27"/>
+      <c r="E140" s="10"/>
     </row>
     <row r="141" ht="15" spans="1:5">
-      <c r="A141" s="24" t="s">
+      <c r="A141" s="22" t="s">
         <v>512</v>
       </c>
-      <c r="B141" s="24" t="s">
+      <c r="B141" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="C141" s="30" t="s">
+      <c r="C141" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="D141" s="26" t="s">
+      <c r="D141" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="E141" s="27"/>
+      <c r="E141" s="10"/>
     </row>
     <row r="142" ht="15" spans="1:5">
-      <c r="A142" s="24" t="s">
+      <c r="A142" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="B142" s="24" t="s">
+      <c r="B142" s="22" t="s">
         <v>517</v>
       </c>
-      <c r="C142" s="28" t="s">
+      <c r="C142" s="22" t="s">
         <v>518</v>
       </c>
-      <c r="D142" s="26" t="s">
+      <c r="D142" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="E142" s="27"/>
+      <c r="E142" s="10"/>
     </row>
     <row r="143" ht="15" spans="1:5">
-      <c r="A143" s="24" t="s">
+      <c r="A143" s="22" t="s">
         <v>520</v>
       </c>
-      <c r="B143" s="24" t="s">
+      <c r="B143" s="22" t="s">
         <v>521</v>
       </c>
-      <c r="C143" s="28" t="s">
+      <c r="C143" s="22" t="s">
         <v>522</v>
       </c>
-      <c r="D143" s="26" t="s">
+      <c r="D143" s="9" t="s">
         <v>523</v>
       </c>
-      <c r="E143" s="27"/>
+      <c r="E143" s="10"/>
     </row>
     <row r="144" ht="15" spans="1:5">
-      <c r="A144" s="24" t="s">
+      <c r="A144" s="22" t="s">
         <v>524</v>
       </c>
-      <c r="B144" s="24" t="s">
+      <c r="B144" s="22" t="s">
         <v>525</v>
       </c>
-      <c r="C144" s="30" t="s">
+      <c r="C144" s="22" t="s">
         <v>526</v>
       </c>
-      <c r="D144" s="26" t="s">
+      <c r="D144" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="E144" s="27"/>
+      <c r="E144" s="10"/>
     </row>
     <row r="145" ht="15" spans="1:5">
-      <c r="A145" s="24" t="s">
+      <c r="A145" s="22" t="s">
         <v>527</v>
       </c>
-      <c r="B145" s="24" t="s">
+      <c r="B145" s="22" t="s">
         <v>528</v>
       </c>
-      <c r="C145" s="28" t="s">
+      <c r="C145" s="22" t="s">
         <v>529</v>
       </c>
-      <c r="D145" s="26" t="s">
+      <c r="D145" s="9" t="s">
         <v>530</v>
       </c>
-      <c r="E145" s="27"/>
+      <c r="E145" s="10"/>
     </row>
     <row r="146" ht="15" spans="1:5">
-      <c r="A146" s="24" t="s">
+      <c r="A146" s="22" t="s">
         <v>531</v>
       </c>
-      <c r="B146" s="24" t="s">
+      <c r="B146" s="22" t="s">
         <v>532</v>
       </c>
-      <c r="C146" s="28" t="s">
+      <c r="C146" s="22" t="s">
         <v>533</v>
       </c>
-      <c r="D146" s="26" t="s">
+      <c r="D146" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="E146" s="27"/>
+      <c r="E146" s="10"/>
     </row>
     <row r="147" ht="15" spans="1:5">
-      <c r="A147" s="24" t="s">
+      <c r="A147" s="22" t="s">
         <v>535</v>
       </c>
-      <c r="B147" s="24" t="s">
+      <c r="B147" s="22" t="s">
         <v>536</v>
       </c>
-      <c r="C147" s="30" t="s">
+      <c r="C147" s="22" t="s">
         <v>537</v>
       </c>
-      <c r="D147" s="26" t="s">
+      <c r="D147" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="E147" s="27"/>
+      <c r="E147" s="10"/>
     </row>
     <row r="148" ht="15" spans="1:5">
-      <c r="A148" s="24" t="s">
+      <c r="A148" s="22" t="s">
         <v>539</v>
       </c>
-      <c r="B148" s="24" t="s">
+      <c r="B148" s="22" t="s">
         <v>540</v>
       </c>
-      <c r="C148" s="28" t="s">
+      <c r="C148" s="22" t="s">
         <v>541</v>
       </c>
-      <c r="D148" s="26" t="s">
+      <c r="D148" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="E148" s="27"/>
+      <c r="E148" s="10"/>
     </row>
     <row r="149" ht="15" spans="1:5">
-      <c r="A149" s="24" t="s">
+      <c r="A149" s="22" t="s">
         <v>542</v>
       </c>
-      <c r="B149" s="24" t="s">
+      <c r="B149" s="22" t="s">
         <v>543</v>
       </c>
-      <c r="C149" s="28" t="s">
+      <c r="C149" s="22" t="s">
         <v>544</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="D149" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="E149" s="27"/>
+      <c r="E149" s="10"/>
     </row>
     <row r="150" ht="15" spans="1:5">
-      <c r="A150" s="24" t="s">
+      <c r="A150" s="22" t="s">
         <v>546</v>
       </c>
-      <c r="B150" s="24" t="s">
+      <c r="B150" s="22" t="s">
         <v>547</v>
       </c>
-      <c r="C150" s="30" t="s">
+      <c r="C150" s="22" t="s">
         <v>548</v>
       </c>
-      <c r="D150" s="26" t="s">
+      <c r="D150" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="E150" s="27"/>
+      <c r="E150" s="10"/>
     </row>
     <row r="151" ht="15" spans="1:5">
-      <c r="A151" s="24" t="s">
+      <c r="A151" s="22" t="s">
         <v>550</v>
       </c>
-      <c r="B151" s="24" t="s">
+      <c r="B151" s="22" t="s">
         <v>551</v>
       </c>
-      <c r="C151" s="28" t="s">
+      <c r="C151" s="22" t="s">
         <v>552</v>
       </c>
-      <c r="D151" s="26" t="s">
+      <c r="D151" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="E151" s="27"/>
+      <c r="E151" s="10"/>
     </row>
     <row r="152" ht="15" spans="1:5">
-      <c r="A152" s="24" t="s">
+      <c r="A152" s="22" t="s">
         <v>554</v>
       </c>
-      <c r="B152" s="24" t="s">
+      <c r="B152" s="22" t="s">
         <v>555</v>
       </c>
-      <c r="C152" s="28" t="s">
+      <c r="C152" s="22" t="s">
         <v>556</v>
       </c>
-      <c r="D152" s="26" t="s">
+      <c r="D152" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="E152" s="27"/>
+      <c r="E152" s="10"/>
     </row>
     <row r="153" ht="15" spans="1:5">
-      <c r="A153" s="24" t="s">
+      <c r="A153" s="22" t="s">
         <v>557</v>
       </c>
-      <c r="B153" s="24" t="s">
+      <c r="B153" s="22" t="s">
         <v>558</v>
       </c>
-      <c r="C153" s="30" t="s">
+      <c r="C153" s="22" t="s">
         <v>559</v>
       </c>
-      <c r="D153" s="26" t="s">
+      <c r="D153" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="E153" s="27"/>
+      <c r="E153" s="10"/>
     </row>
     <row r="154" ht="15" spans="1:5">
-      <c r="A154" s="24" t="s">
+      <c r="A154" s="22" t="s">
         <v>561</v>
       </c>
-      <c r="B154" s="24" t="s">
+      <c r="B154" s="22" t="s">
         <v>562</v>
       </c>
-      <c r="C154" s="28" t="s">
+      <c r="C154" s="22" t="s">
         <v>563</v>
       </c>
-      <c r="D154" s="26" t="s">
+      <c r="D154" s="9" t="s">
         <v>564</v>
       </c>
-      <c r="E154" s="27"/>
+      <c r="E154" s="10"/>
     </row>
     <row r="155" ht="15" spans="1:5">
-      <c r="A155" s="24" t="s">
+      <c r="A155" s="22" t="s">
         <v>565</v>
       </c>
-      <c r="B155" s="24" t="s">
+      <c r="B155" s="22" t="s">
         <v>566</v>
       </c>
-      <c r="C155" s="30" t="s">
+      <c r="C155" s="22" t="s">
         <v>567</v>
       </c>
-      <c r="D155" s="26" t="s">
+      <c r="D155" s="9" t="s">
         <v>568</v>
       </c>
-      <c r="E155" s="27"/>
+      <c r="E155" s="10"/>
     </row>
     <row r="156" ht="15" spans="1:5">
-      <c r="A156" s="24" t="s">
+      <c r="A156" s="22" t="s">
         <v>569</v>
       </c>
-      <c r="B156" s="24" t="s">
+      <c r="B156" s="22" t="s">
         <v>570</v>
       </c>
-      <c r="C156" s="28" t="s">
+      <c r="C156" s="22" t="s">
         <v>571</v>
       </c>
-      <c r="D156" s="26" t="s">
+      <c r="D156" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E156" s="27"/>
+      <c r="E156" s="10"/>
     </row>
     <row r="157" ht="15" spans="1:5">
-      <c r="A157" s="24" t="s">
+      <c r="A157" s="22" t="s">
         <v>572</v>
       </c>
-      <c r="B157" s="24" t="s">
+      <c r="B157" s="22" t="s">
         <v>573</v>
       </c>
-      <c r="C157" s="30" t="s">
+      <c r="C157" s="22" t="s">
         <v>574</v>
       </c>
-      <c r="D157" s="26" t="s">
+      <c r="D157" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="E157" s="27"/>
+      <c r="E157" s="10"/>
     </row>
     <row r="158" ht="15" spans="1:5">
-      <c r="A158" s="24" t="s">
+      <c r="A158" s="22" t="s">
         <v>576</v>
       </c>
-      <c r="B158" s="24" t="s">
+      <c r="B158" s="22" t="s">
         <v>577</v>
       </c>
-      <c r="C158" s="28" t="s">
+      <c r="C158" s="22" t="s">
         <v>578</v>
       </c>
-      <c r="D158" s="26" t="s">
+      <c r="D158" s="9" t="s">
         <v>579</v>
       </c>
-      <c r="E158" s="27"/>
+      <c r="E158" s="10"/>
     </row>
     <row r="159" ht="15" spans="1:5">
-      <c r="A159" s="24" t="s">
+      <c r="A159" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="B159" s="24" t="s">
+      <c r="B159" s="22" t="s">
         <v>580</v>
       </c>
-      <c r="C159" s="30" t="s">
+      <c r="C159" s="22" t="s">
         <v>581</v>
       </c>
-      <c r="D159" s="26" t="s">
+      <c r="D159" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="E159" s="27"/>
+      <c r="E159" s="10"/>
     </row>
     <row r="160" ht="15" spans="1:5">
-      <c r="A160" s="24" t="s">
+      <c r="A160" s="22" t="s">
         <v>583</v>
       </c>
-      <c r="B160" s="24" t="s">
+      <c r="B160" s="22" t="s">
         <v>584</v>
       </c>
-      <c r="C160" s="28" t="s">
+      <c r="C160" s="22" t="s">
         <v>585</v>
       </c>
-      <c r="D160" s="26" t="s">
+      <c r="D160" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E160" s="27"/>
+      <c r="E160" s="10"/>
     </row>
     <row r="161" ht="15" spans="1:5">
-      <c r="A161" s="24" t="s">
+      <c r="A161" s="22" t="s">
         <v>586</v>
       </c>
-      <c r="B161" s="24" t="s">
+      <c r="B161" s="22" t="s">
         <v>587</v>
       </c>
-      <c r="C161" s="30" t="s">
+      <c r="C161" s="22" t="s">
         <v>588</v>
       </c>
-      <c r="D161" s="26" t="s">
+      <c r="D161" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="E161" s="27"/>
+      <c r="E161" s="10"/>
     </row>
     <row r="162" ht="15" spans="1:5">
-      <c r="A162" s="24" t="s">
+      <c r="A162" s="22" t="s">
         <v>590</v>
       </c>
-      <c r="B162" s="24" t="s">
+      <c r="B162" s="22" t="s">
         <v>591</v>
       </c>
-      <c r="C162" s="28" t="s">
+      <c r="C162" s="22" t="s">
         <v>592</v>
       </c>
-      <c r="D162" s="26" t="s">
+      <c r="D162" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="E162" s="27"/>
+      <c r="E162" s="10"/>
     </row>
     <row r="163" ht="15" spans="1:5">
-      <c r="A163" s="24" t="s">
+      <c r="A163" s="22" t="s">
         <v>594</v>
       </c>
-      <c r="B163" s="25" t="s">
+      <c r="B163" s="22" t="s">
         <v>595</v>
       </c>
-      <c r="C163" s="28" t="s">
+      <c r="C163" s="22" t="s">
         <v>596</v>
       </c>
-      <c r="D163" s="26" t="s">
+      <c r="D163" s="9" t="s">
         <v>597</v>
       </c>
-      <c r="E163" s="27"/>
+      <c r="E163" s="10"/>
     </row>
     <row r="164" ht="15" spans="1:5">
-      <c r="A164" s="24" t="s">
+      <c r="A164" s="22" t="s">
         <v>598</v>
       </c>
-      <c r="B164" s="25" t="s">
+      <c r="B164" s="22" t="s">
         <v>599</v>
       </c>
-      <c r="C164" s="28" t="s">
+      <c r="C164" s="22" t="s">
         <v>600</v>
       </c>
-      <c r="D164" s="26" t="s">
+      <c r="D164" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="E164" s="27"/>
+      <c r="E164" s="10"/>
     </row>
     <row r="165" ht="15" spans="1:5">
-      <c r="A165" s="23" t="s">
+      <c r="A165" s="22" t="s">
         <v>601</v>
       </c>
-      <c r="B165" s="22" t="s">
+      <c r="B165" s="21" t="s">
         <v>602</v>
       </c>
-      <c r="C165" s="22" t="s">
+      <c r="C165" s="21" t="s">
         <v>603</v>
       </c>
-      <c r="D165" s="31" t="s">
+      <c r="D165" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="E165" s="11"/>
+      <c r="E165" s="10"/>
     </row>
     <row r="166" ht="15" spans="1:5">
-      <c r="A166" s="23" t="s">
+      <c r="A166" s="22" t="s">
         <v>605</v>
       </c>
-      <c r="B166" s="22" t="s">
+      <c r="B166" s="21" t="s">
         <v>606</v>
       </c>
-      <c r="C166" s="22" t="s">
+      <c r="C166" s="21" t="s">
         <v>607</v>
       </c>
-      <c r="D166" s="10" t="s">
+      <c r="D166" s="9" t="s">
         <v>608</v>
       </c>
-      <c r="E166" s="11"/>
+      <c r="E166" s="10"/>
     </row>
     <row r="167" ht="15" spans="1:5">
-      <c r="A167" s="23" t="s">
+      <c r="A167" s="22" t="s">
         <v>609</v>
       </c>
-      <c r="B167" s="23" t="s">
+      <c r="B167" s="22" t="s">
         <v>610</v>
       </c>
-      <c r="C167" s="22" t="s">
+      <c r="C167" s="21" t="s">
         <v>611</v>
       </c>
-      <c r="D167" s="31" t="s">
+      <c r="D167" s="9" t="s">
         <v>612</v>
       </c>
-      <c r="E167" s="11"/>
+      <c r="E167" s="10"/>
     </row>
     <row r="168" ht="15" spans="1:5">
-      <c r="A168" s="22" t="s">
+      <c r="A168" s="21" t="s">
         <v>613</v>
       </c>
-      <c r="B168" s="23" t="s">
+      <c r="B168" s="22" t="s">
         <v>614</v>
       </c>
-      <c r="C168" s="22" t="s">
+      <c r="C168" s="21" t="s">
         <v>615</v>
       </c>
-      <c r="D168" s="10" t="s">
+      <c r="D168" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E168" s="11"/>
+      <c r="E168" s="10"/>
     </row>
     <row r="169" ht="15" spans="1:5">
-      <c r="A169" s="23" t="s">
+      <c r="A169" s="22" t="s">
         <v>616</v>
       </c>
-      <c r="B169" s="23" t="s">
+      <c r="B169" s="22" t="s">
         <v>617</v>
       </c>
-      <c r="C169" s="22" t="s">
+      <c r="C169" s="21" t="s">
         <v>618</v>
       </c>
-      <c r="D169" s="31" t="s">
+      <c r="D169" s="9" t="s">
         <v>619</v>
       </c>
-      <c r="E169" s="11"/>
+      <c r="E169" s="10"/>
     </row>
     <row r="170" ht="15" spans="1:5">
-      <c r="A170" s="23" t="s">
+      <c r="A170" s="22" t="s">
         <v>620</v>
       </c>
-      <c r="B170" s="22" t="s">
+      <c r="B170" s="21" t="s">
         <v>621</v>
       </c>
-      <c r="C170" s="22" t="s">
+      <c r="C170" s="21" t="s">
         <v>622</v>
       </c>
-      <c r="D170" s="10" t="s">
+      <c r="D170" s="9" t="s">
         <v>623</v>
       </c>
-      <c r="E170" s="11"/>
+      <c r="E170" s="10"/>
     </row>
     <row r="171" ht="15" spans="1:5">
-      <c r="A171" s="23" t="s">
+      <c r="A171" s="22" t="s">
         <v>624</v>
       </c>
-      <c r="B171" s="22" t="s">
+      <c r="B171" s="21" t="s">
         <v>625</v>
       </c>
-      <c r="C171" s="22" t="s">
+      <c r="C171" s="21" t="s">
         <v>626</v>
       </c>
-      <c r="D171" s="31" t="s">
+      <c r="D171" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="E171" s="11"/>
+      <c r="E171" s="10"/>
     </row>
     <row r="172" ht="15" spans="1:5">
-      <c r="A172" s="23" t="s">
+      <c r="A172" s="22" t="s">
         <v>628</v>
       </c>
-      <c r="B172" s="23" t="s">
+      <c r="B172" s="22" t="s">
         <v>629</v>
       </c>
-      <c r="C172" s="22" t="s">
+      <c r="C172" s="21" t="s">
         <v>630</v>
       </c>
-      <c r="D172" s="10" t="s">
+      <c r="D172" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E172" s="11"/>
+      <c r="E172" s="10"/>
     </row>
     <row r="173" ht="15" spans="1:5">
-      <c r="A173" s="23" t="s">
+      <c r="A173" s="22" t="s">
         <v>631</v>
       </c>
-      <c r="B173" s="23" t="s">
+      <c r="B173" s="22" t="s">
         <v>632</v>
       </c>
-      <c r="C173" s="22" t="s">
+      <c r="C173" s="21" t="s">
         <v>633</v>
       </c>
-      <c r="D173" s="31" t="s">
+      <c r="D173" s="9" t="s">
         <v>634</v>
       </c>
-      <c r="E173" s="11"/>
+      <c r="E173" s="10"/>
     </row>
     <row r="174" ht="15" spans="1:5">
-      <c r="A174" s="23" t="s">
+      <c r="A174" s="22" t="s">
         <v>635</v>
       </c>
-      <c r="B174" s="23" t="s">
+      <c r="B174" s="22" t="s">
         <v>636</v>
       </c>
-      <c r="C174" s="22" t="s">
+      <c r="C174" s="21" t="s">
         <v>637</v>
       </c>
-      <c r="D174" s="10" t="s">
+      <c r="D174" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="E174" s="11"/>
+      <c r="E174" s="10"/>
     </row>
     <row r="175" ht="15" spans="1:5">
-      <c r="A175" s="23" t="s">
+      <c r="A175" s="22" t="s">
         <v>639</v>
       </c>
-      <c r="B175" s="22" t="s">
+      <c r="B175" s="21" t="s">
         <v>640</v>
       </c>
-      <c r="C175" s="22" t="s">
+      <c r="C175" s="21" t="s">
         <v>641</v>
       </c>
-      <c r="D175" s="31" t="s">
+      <c r="D175" s="9" t="s">
         <v>642</v>
       </c>
-      <c r="E175" s="11"/>
+      <c r="E175" s="10"/>
     </row>
     <row r="176" ht="15" spans="1:5">
-      <c r="A176" s="23" t="s">
+      <c r="A176" s="22" t="s">
         <v>643</v>
       </c>
-      <c r="B176" s="22" t="s">
+      <c r="B176" s="21" t="s">
         <v>644</v>
       </c>
-      <c r="C176" s="22" t="s">
+      <c r="C176" s="21" t="s">
         <v>645</v>
       </c>
-      <c r="D176" s="10" t="s">
+      <c r="D176" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E176" s="11"/>
+      <c r="E176" s="10"/>
     </row>
     <row r="177" ht="15" spans="1:5">
-      <c r="A177" s="23" t="s">
+      <c r="A177" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="B177" s="23" t="s">
+      <c r="B177" s="22" t="s">
         <v>647</v>
       </c>
-      <c r="C177" s="22" t="s">
+      <c r="C177" s="21" t="s">
         <v>648</v>
       </c>
-      <c r="D177" s="31" t="s">
+      <c r="D177" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="E177" s="11"/>
+      <c r="E177" s="10"/>
     </row>
     <row r="178" ht="15" spans="1:5">
-      <c r="A178" s="23" t="s">
+      <c r="A178" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="B178" s="23" t="s">
+      <c r="B178" s="22" t="s">
         <v>651</v>
       </c>
-      <c r="C178" s="22" t="s">
+      <c r="C178" s="21" t="s">
         <v>652</v>
       </c>
-      <c r="D178" s="10" t="s">
+      <c r="D178" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="E178" s="11"/>
+      <c r="E178" s="10"/>
     </row>
     <row r="179" ht="15" spans="1:5">
-      <c r="A179" s="23"/>
-      <c r="B179" s="23"/>
-      <c r="C179" s="22"/>
-      <c r="D179" s="31"/>
-      <c r="E179" s="11"/>
+      <c r="A179" s="22"/>
+      <c r="B179" s="22"/>
+      <c r="C179" s="21"/>
+      <c r="D179" s="9"/>
+      <c r="E179" s="10"/>
     </row>
     <row r="180" ht="15" spans="1:5">
-      <c r="A180" s="22"/>
-      <c r="B180" s="23"/>
-      <c r="C180" s="22"/>
-      <c r="D180" s="10"/>
-      <c r="E180" s="11"/>
+      <c r="A180" s="21"/>
+      <c r="B180" s="22"/>
+      <c r="C180" s="21"/>
+      <c r="D180" s="9"/>
+      <c r="E180" s="10"/>
     </row>
     <row r="181" ht="15" spans="1:5">
-      <c r="A181" s="22"/>
-      <c r="B181" s="23"/>
-      <c r="C181" s="32"/>
-      <c r="D181" s="31"/>
-      <c r="E181" s="11"/>
+      <c r="A181" s="21"/>
+      <c r="B181" s="22"/>
+      <c r="C181" s="23"/>
+      <c r="D181" s="9"/>
+      <c r="E181" s="10"/>
     </row>
     <row r="182" ht="15" spans="1:5">
-      <c r="A182" s="22"/>
-      <c r="B182" s="23"/>
-      <c r="C182" s="20"/>
-      <c r="D182" s="10"/>
-      <c r="E182" s="11"/>
+      <c r="A182" s="21"/>
+      <c r="B182" s="22"/>
+      <c r="C182" s="19"/>
+      <c r="D182" s="9"/>
+      <c r="E182" s="10"/>
     </row>
     <row r="183" ht="15" spans="1:5">
-      <c r="A183" s="22"/>
-      <c r="B183" s="23"/>
-      <c r="C183" s="32"/>
-      <c r="D183" s="31"/>
-      <c r="E183" s="11"/>
+      <c r="A183" s="21"/>
+      <c r="B183" s="22"/>
+      <c r="C183" s="23"/>
+      <c r="D183" s="9"/>
+      <c r="E183" s="10"/>
     </row>
     <row r="184" ht="15" spans="1:5">
-      <c r="A184" s="22"/>
-      <c r="B184" s="23"/>
-      <c r="C184" s="20"/>
-      <c r="D184" s="10"/>
-      <c r="E184" s="11"/>
+      <c r="A184" s="21"/>
+      <c r="B184" s="22"/>
+      <c r="C184" s="19"/>
+      <c r="D184" s="9"/>
+      <c r="E184" s="10"/>
     </row>
     <row r="185" ht="15" spans="1:5">
-      <c r="A185" s="22"/>
-      <c r="B185" s="23"/>
-      <c r="C185" s="32"/>
-      <c r="D185" s="31"/>
-      <c r="E185" s="11"/>
+      <c r="A185" s="21"/>
+      <c r="B185" s="22"/>
+      <c r="C185" s="23"/>
+      <c r="D185" s="9"/>
+      <c r="E185" s="10"/>
     </row>
     <row r="186" ht="15" spans="1:5">
-      <c r="A186" s="22"/>
-      <c r="B186" s="23"/>
-      <c r="C186" s="20"/>
-      <c r="D186" s="10"/>
-      <c r="E186" s="11"/>
+      <c r="A186" s="21"/>
+      <c r="B186" s="22"/>
+      <c r="C186" s="19"/>
+      <c r="D186" s="9"/>
+      <c r="E186" s="10"/>
     </row>
     <row r="187" ht="15" spans="1:5">
-      <c r="A187" s="22"/>
-      <c r="B187" s="23"/>
-      <c r="C187" s="32"/>
-      <c r="D187" s="31"/>
-      <c r="E187" s="11"/>
+      <c r="A187" s="21"/>
+      <c r="B187" s="22"/>
+      <c r="C187" s="23"/>
+      <c r="D187" s="9"/>
+      <c r="E187" s="10"/>
     </row>
     <row r="188" ht="15" spans="1:5">
-      <c r="A188" s="22"/>
-      <c r="B188" s="23"/>
-      <c r="C188" s="20"/>
-      <c r="D188" s="10"/>
-      <c r="E188" s="11"/>
+      <c r="A188" s="21"/>
+      <c r="B188" s="22"/>
+      <c r="C188" s="19"/>
+      <c r="D188" s="9"/>
+      <c r="E188" s="10"/>
     </row>
     <row r="189" ht="15" spans="1:5">
-      <c r="A189" s="22"/>
-      <c r="B189" s="23"/>
-      <c r="C189" s="32"/>
-      <c r="D189" s="31"/>
-      <c r="E189" s="11"/>
+      <c r="A189" s="21"/>
+      <c r="B189" s="22"/>
+      <c r="C189" s="23"/>
+      <c r="D189" s="9"/>
+      <c r="E189" s="10"/>
     </row>
     <row r="190" ht="15" spans="1:5">
-      <c r="A190" s="22"/>
-      <c r="B190" s="23"/>
-      <c r="C190" s="20"/>
-      <c r="D190" s="10"/>
-      <c r="E190" s="11"/>
+      <c r="A190" s="21"/>
+      <c r="B190" s="22"/>
+      <c r="C190" s="19"/>
+      <c r="D190" s="9"/>
+      <c r="E190" s="10"/>
     </row>
     <row r="191" ht="15" spans="1:5">
-      <c r="A191" s="22"/>
-      <c r="B191" s="23"/>
-      <c r="C191" s="32"/>
-      <c r="D191" s="31"/>
-      <c r="E191" s="11"/>
+      <c r="A191" s="21"/>
+      <c r="B191" s="22"/>
+      <c r="C191" s="23"/>
+      <c r="D191" s="9"/>
+      <c r="E191" s="10"/>
     </row>
     <row r="192" ht="15" spans="1:5">
-      <c r="A192" s="22"/>
-      <c r="B192" s="23"/>
-      <c r="C192" s="20"/>
-      <c r="D192" s="10"/>
-      <c r="E192" s="11"/>
+      <c r="A192" s="21"/>
+      <c r="B192" s="22"/>
+      <c r="C192" s="19"/>
+      <c r="D192" s="9"/>
+      <c r="E192" s="10"/>
     </row>
     <row r="193" ht="14.25" spans="1:5">
-      <c r="A193" s="22"/>
-      <c r="B193" s="23"/>
-      <c r="C193" s="32"/>
-      <c r="D193" s="31"/>
-      <c r="E193" s="11"/>
+      <c r="A193" s="21"/>
+      <c r="B193" s="22"/>
+      <c r="C193" s="23"/>
+      <c r="D193" s="9"/>
+      <c r="E193" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="189">
